--- a/UH15-Series/UH15-16/UH15-16_Crypto infection inhibition_TUFTS.xlsx
+++ b/UH15-Series/UH15-16/UH15-16_Crypto infection inhibition_TUFTS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddayao01/Library/CloudStorage/Box-Box/R01 Evaluation of CDPK1 inhibitors_Crypto in vitro/Data for Greg_January 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddayao01/Library/CloudStorage/Box-Box/DD Shared Folder 2026/Cryptosporidium/R01 Evaluation of CDPK1 inhibitors_Crypto in vitro/Data for Greg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F53F29F-DA8B-9F4D-92C5-DCAE333C82C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436C910D-137B-D24D-BD68-B47608ABFC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16300" activeTab="1" xr2:uid="{54FBB44D-0A49-0E43-88E7-D7DBB30D6BBA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="11">
   <si>
     <t>Well 1</t>
   </si>
@@ -123,13 +123,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +481,18 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
@@ -522,9 +522,9 @@
       <c r="F7" s="1">
         <v>93.102526983296116</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
@@ -542,9 +542,9 @@
       <c r="F8" s="1">
         <v>90.703405934007833</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
@@ -562,9 +562,9 @@
       <c r="F9" s="1">
         <v>87.295563534450551</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -582,9 +582,9 @@
       <c r="F10" s="1">
         <v>86.341367662574541</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
@@ -602,9 +602,9 @@
       <c r="F11" s="1">
         <v>86.941147924896612</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
@@ -622,9 +622,9 @@
       <c r="F12" s="1">
         <v>85.523485486680784</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
@@ -642,9 +642,9 @@
       <c r="F13" s="1">
         <v>66.303254353177877</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
@@ -662,9 +662,9 @@
       <c r="F14" s="1">
         <v>13.11365018088828</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
@@ -682,9 +682,9 @@
       <c r="F15" s="1">
         <v>-15.648539671374934</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
@@ -702,9 +702,9 @@
       <c r="F16" s="1">
         <v>2.7262739197049984E-4</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
@@ -712,18 +712,18 @@
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2" t="s">
         <v>0</v>
       </c>
@@ -938,18 +938,18 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
@@ -967,228 +967,392 @@
       <c r="B7" s="1">
         <v>25</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="3">
         <v>96.369882000000004</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>97.29095667</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>96.424062800000002</v>
       </c>
       <c r="F7">
         <v>96.694967139304424</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>8.3333333333333339</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="3">
         <v>96.803329000000005</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>96.478243669999998</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>96.369881899999996</v>
       </c>
       <c r="F8">
         <v>96.550484828454344</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>2.7777777777777781</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <v>94.961179000000001</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>94.690275080000006</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <v>94.527732499999999</v>
       </c>
       <c r="F9">
         <v>94.726395653972091</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="3"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>0.92592592592592604</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="3">
         <v>92.143773999999993</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>92.956487350000003</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="3">
         <v>91.331061300000002</v>
       </c>
       <c r="F10">
         <v>92.143774347526914</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>0.30864197530864201</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="3">
         <v>90.735072000000002</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>92.360497809999998</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="3">
         <v>90.572529200000005</v>
       </c>
       <c r="F11">
         <v>91.222699615857664</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>0.10288065843621401</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>83.854101999999997</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>85.750432090000004</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="3">
         <v>80.223983700000005</v>
       </c>
       <c r="F12">
         <v>83.27617251910327</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>3.4293552812071339E-2</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="3">
         <v>50.207783999999997</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <v>41.593025840000003</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="3">
         <v>52.645922599999999</v>
       </c>
       <c r="F13">
         <v>48.148910693677635</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
         <v>1.1431184270690446E-2</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="3">
         <v>11.143378999999999</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <v>15.206943819999999</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <v>15.5500893</v>
       </c>
       <c r="F14">
         <v>13.966803985062938</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
         <v>3.8103947568968156E-3</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="3">
         <v>7.5132608000000003</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="3">
         <v>4.4249513729999999</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="3">
         <v>6.8089095000000004</v>
       </c>
       <c r="F15">
         <v>6.2490405471545145</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <v>0</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="3">
         <v>-7.2060600000000002E-2</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="3">
         <v>-5.056700277</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="3">
         <v>5.1293026399999997</v>
       </c>
       <c r="F16">
         <v>1.8060288856662035E-4</v>
       </c>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="19" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B22" s="1"/>
+      <c r="B22" s="1">
+        <v>25</v>
+      </c>
+      <c r="C22" s="3">
+        <v>95.867344000000003</v>
+      </c>
+      <c r="D22" s="3">
+        <v>95.845478020000002</v>
+      </c>
+      <c r="E22" s="3">
+        <v>95.954807500000001</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22:F30" si="0">AVERAGE(C22:E22)</f>
+        <v>95.889209839999992</v>
+      </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B23" s="1"/>
+      <c r="B23" s="1">
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="C23" s="3">
+        <v>95.386294000000007</v>
+      </c>
+      <c r="D23" s="3">
+        <v>95.298830390000006</v>
+      </c>
+      <c r="E23" s="3">
+        <v>95.364428099999998</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>95.349850829999994</v>
+      </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
+      <c r="B24" s="1">
+        <v>2.7777777777777781</v>
+      </c>
+      <c r="C24" s="3">
+        <v>94.402327999999997</v>
+      </c>
+      <c r="D24" s="3">
+        <v>94.70845095</v>
+      </c>
+      <c r="E24" s="3">
+        <v>96.020405299999993</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>95.043728083333335</v>
+      </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B25" s="1"/>
+      <c r="B25" s="1">
+        <v>0.92592592592592604</v>
+      </c>
+      <c r="C25" s="3">
+        <v>90.553928999999997</v>
+      </c>
+      <c r="D25" s="3">
+        <v>91.9533469</v>
+      </c>
+      <c r="E25" s="3">
+        <v>89.613695100000001</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>90.706990333333337</v>
+      </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B26" s="1"/>
+      <c r="B26" s="1">
+        <v>0.30864197530864201</v>
+      </c>
+      <c r="C26" s="3">
+        <v>87.886289000000005</v>
+      </c>
+      <c r="D26" s="3">
+        <v>87.055384149999995</v>
+      </c>
+      <c r="E26" s="3">
+        <v>87.776959000000005</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>87.572877383333321</v>
+      </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B27" s="1"/>
+      <c r="B27" s="1">
+        <v>0.10288065843621401</v>
+      </c>
+      <c r="C27" s="3">
+        <v>76.472285999999997</v>
+      </c>
+      <c r="D27" s="3">
+        <v>73.257998000000001</v>
+      </c>
+      <c r="E27" s="3">
+        <v>68.053912600000004</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>72.594732199999996</v>
+      </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B28" s="1"/>
+      <c r="B28" s="1">
+        <v>3.4293552812071339E-2</v>
+      </c>
+      <c r="C28" s="3">
+        <v>35.736105000000002</v>
+      </c>
+      <c r="D28" s="3">
+        <v>40.634067520000002</v>
+      </c>
+      <c r="E28" s="3">
+        <v>42.492669499999998</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>39.620947340000008</v>
+      </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="1"/>
+      <c r="B29" s="1">
+        <v>1.1431184270690446E-2</v>
+      </c>
+      <c r="C29" s="3">
+        <v>20.211312</v>
+      </c>
+      <c r="D29" s="3">
+        <v>18.002855690000001</v>
+      </c>
+      <c r="E29" s="3">
+        <v>15.510142500000001</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>17.908103396666665</v>
+      </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B30" s="1"/>
+      <c r="B30" s="1">
+        <v>3.8103947568968156E-3</v>
+      </c>
+      <c r="C30" s="3">
+        <v>11.115095999999999</v>
+      </c>
+      <c r="D30" s="3">
+        <v>16.10052194</v>
+      </c>
+      <c r="E30" s="3">
+        <v>16.187985600000001</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>14.467867846666669</v>
+      </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B31" s="1"/>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3">
+        <v>-10.16043</v>
+      </c>
+      <c r="D31" s="3">
+        <v>8.5130528519999995</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1.6471586300000001</v>
+      </c>
+      <c r="F31">
+        <f>C31+D31+E31</f>
+        <v>-2.1851800000027843E-4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
